--- a/backend/db/data/Form/경비정산서 양식.xlsx
+++ b/backend/db/data/Form/경비정산서 양식.xlsx
@@ -5,91 +5,63 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cwy/Documents/CWY/Work/AI_Agent/PJT/whattodo/backend/db/data/Form/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cwy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A3EA03-36A2-5A49-8296-8456C2BA3AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50429907-9108-C44E-B812-470EBA52C9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="600" windowWidth="28100" windowHeight="16140" xr2:uid="{512DD689-413B-8F43-AF20-A1A8B05DE068}"/>
+    <workbookView xWindow="340" yWindow="600" windowWidth="28100" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>출장 여비 정산서</t>
+  </si>
+  <si>
+    <t>출장 일정</t>
+  </si>
+  <si>
+    <t>2026년   월   일 ~ 2026년   월   일</t>
+  </si>
+  <si>
+    <t>소속</t>
+  </si>
   <si>
     <t>성명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출장 여비 정산서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소속</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>출장 지역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>출장 목적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 날짜</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>사용 금액</t>
+  </si>
+  <si>
+    <t>비고</t>
   </si>
   <si>
     <t>내역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 날짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>경비 총액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026년   월   일 ~ 2026년   월   일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출장 일정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>분류</t>
+  </si>
+  <si>
+    <t>특이사항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -169,17 +141,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -249,17 +210,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -311,19 +261,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -354,10 +291,25 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -368,9 +320,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -386,70 +336,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -785,7 +703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5ADE18-50BA-C04B-960D-47C346487D03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
@@ -808,18 +726,18 @@
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="2:17" ht="18" customHeight="1">
-      <c r="B3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="16"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -828,16 +746,16 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="2:17" ht="18" customHeight="1">
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -846,16 +764,16 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="2:17" ht="18" customHeight="1" thickBot="1">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -881,20 +799,20 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="2:17" ht="18" customHeight="1">
-      <c r="B7" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="7"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -902,110 +820,110 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="2:17">
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="2:17">
-      <c r="B9" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="2:17">
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="2:17">
-      <c r="B11" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="2:17">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="2:17">
-      <c r="B13" s="22"/>
-      <c r="C13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="5" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="5" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="2:17">
-      <c r="B14" s="23"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="8"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="2:17" ht="20" customHeight="1">
-      <c r="B15" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="23"/>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
@@ -1016,7 +934,7 @@
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="2:17" ht="20" customHeight="1">
-      <c r="B16" s="11"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="2"/>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
@@ -1028,7 +946,7 @@
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="2:11" ht="20" customHeight="1">
-      <c r="B17" s="11"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
       <c r="E17" s="2"/>
@@ -1040,7 +958,7 @@
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="2:11" ht="20" customHeight="1">
-      <c r="B18" s="11"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
       <c r="E18" s="2"/>
@@ -1052,7 +970,7 @@
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="2:11" ht="20" customHeight="1">
-      <c r="B19" s="11"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
@@ -1064,7 +982,7 @@
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="2:11" ht="20" customHeight="1">
-      <c r="B20" s="11"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
       <c r="E20" s="2"/>
@@ -1076,7 +994,7 @@
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="2:11" ht="20" customHeight="1">
-      <c r="B21" s="11"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
       <c r="E21" s="2"/>
@@ -1088,7 +1006,7 @@
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="2:11" ht="20" customHeight="1">
-      <c r="B22" s="11"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
@@ -1100,7 +1018,7 @@
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="2:11" ht="20" customHeight="1">
-      <c r="B23" s="11"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="2"/>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
@@ -1112,7 +1030,7 @@
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="2:11" ht="20" customHeight="1">
-      <c r="B24" s="11"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="2"/>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
@@ -1124,7 +1042,7 @@
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="2:11" ht="20" customHeight="1">
-      <c r="B25" s="11"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="2"/>
       <c r="D25" s="3"/>
       <c r="E25" s="2"/>
@@ -1136,7 +1054,7 @@
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="2:11" ht="20" customHeight="1">
-      <c r="B26" s="11"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="2"/>
@@ -1148,7 +1066,7 @@
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="2:11" ht="20" customHeight="1">
-      <c r="B27" s="11"/>
+      <c r="B27" s="13"/>
       <c r="C27" s="2"/>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
@@ -1160,7 +1078,7 @@
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="2:11" ht="20" customHeight="1">
-      <c r="B28" s="11"/>
+      <c r="B28" s="13"/>
       <c r="C28" s="2"/>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
@@ -1172,7 +1090,7 @@
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="2:11" ht="20" customHeight="1">
-      <c r="B29" s="11"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="2"/>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
@@ -1184,7 +1102,7 @@
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="2:11" ht="20" customHeight="1">
-      <c r="B30" s="11"/>
+      <c r="B30" s="13"/>
       <c r="C30" s="2"/>
       <c r="D30" s="3"/>
       <c r="E30" s="2"/>
@@ -1196,7 +1114,7 @@
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="2:11" ht="20" customHeight="1">
-      <c r="B31" s="11"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="2"/>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
@@ -1208,7 +1126,7 @@
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="2:11" ht="20" customHeight="1">
-      <c r="B32" s="11"/>
+      <c r="B32" s="13"/>
       <c r="C32" s="2"/>
       <c r="D32" s="3"/>
       <c r="E32" s="2"/>
@@ -1220,7 +1138,7 @@
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="2:11" ht="20" customHeight="1">
-      <c r="B33" s="11"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="2"/>
       <c r="D33" s="3"/>
       <c r="E33" s="2"/>
@@ -1232,7 +1150,7 @@
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="2:11" ht="20" customHeight="1">
-      <c r="B34" s="11"/>
+      <c r="B34" s="12"/>
       <c r="C34" s="2"/>
       <c r="D34" s="3"/>
       <c r="E34" s="2"/>
@@ -1244,133 +1162,136 @@
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" spans="2:11">
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="101">
+    <mergeCell ref="D35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:K36"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I13:K14"/>
+    <mergeCell ref="E21:F21"/>
     <mergeCell ref="B3:K5"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="D9:F10"/>
-    <mergeCell ref="I9:K10"/>
-    <mergeCell ref="D7:K8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:H12"/>
-    <mergeCell ref="I11:K12"/>
-    <mergeCell ref="B15:B34"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="I31:K31"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="D35:G36"/>
-    <mergeCell ref="H35:K36"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="I15:K15"/>
     <mergeCell ref="E13:F14"/>
     <mergeCell ref="G13:H14"/>
-    <mergeCell ref="I13:K14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:K31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="B15:B34"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="I9:K10"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="I11:K12"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I19:K19"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G9:H10"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="G11:H12"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="I34:K34"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="D7:K8"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="G24:H24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
